--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Observation-results-laboratory-pathology-uv-ips</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -272,14 +269,14 @@
 </t>
   </si>
   <si>
-    <t>This observation may represent the result of a simple laboratory or pathology test such as hematocrit, or it may group the set of results produced by a multi-test study or panel such as a complete blood count, a dynamic function test, or a urine specimen study. In the latter case, the observation carries the overall conclusion of the study and references the atomic results of the study as "has-member" child observations</t>
-  </si>
-  <si>
-    <t>Represents either a lab simple observation or the group of observations produced by a laboratory study.</t>
+    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+  </si>
+  <si>
+    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ips-2:At least one of these Observation elements shall be provided:  "value", "dataAbsentReason", "hasMember" or "component" {value.exists() or hasMember.exists() or component.exists() or dataAbsentReason.exists()}ips-3:If observation has components, at least one of these Observation.component elements shall be provided:  "value" or "dataAbsentReason" {component.exists() implies (component.value.exists() or component.dataAbsentReason.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -570,9 +567,6 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Observation 'complete' status codes</t>
-  </si>
-  <si>
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
@@ -588,7 +582,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-status-uv-ips</t>
+    <t>Codes providing the status of an observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -607,87 +604,54 @@
   </si>
   <si>
     <t>Observation.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made. In this profile, fixed to "laboratory".</t>
-  </si>
-  <si>
-    <t>"laboratory" includes laboratory medicine and pathology</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory</t>
-  </si>
-  <si>
-    <t>laboratory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="laboratory"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Concept - reference to a terminology or just  text</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".  In this profile this code represents either a simple laboratory test or a single pathology examination or a laboratory or pathology study with multiple child observations.</t>
-  </si>
-  <si>
-    <t>In the context of this Observation-results-laboratory-pathology-uv-ips profile, when the observation plays the role of a grouper of member sub-observations, the code represents the group (for instance a panel code). In case no code is available, at least a text shall be provided.</t>
+    <t>Type of observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -696,14 +660,22 @@
     <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -716,8 +688,7 @@
     <t>Who and/or what the observation is about</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device whose characteristics (direct or indirect) are described by the observation and into whose record the observation is placed.  Comments: Indirect characteristics may be those of a specimen, fetus, donor, other observer (for example a relative or EMT), or any observation made about the subject.
-In this profile is constrained to the patient</t>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -738,7 +709,434 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
-    <t>Observation.subject.id</t>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>What the observation is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter)
+</t>
+  </si>
+  <si>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
+</t>
+  </si>
+  <si>
+    <t>dateTime
+PeriodTiminginstant</t>
+  </si>
+  <si>
+    <t>Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-organization|CareTeam|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
+    <t>&lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>OBX.2, OBX.5, OBX.6</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-coded-values-laboratory-pathology-uv-ips</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+  </si>
+  <si>
+    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
+</t>
+  </si>
+  <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abnormal Flag
+</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-observationinterpretation</t>
+  </si>
+  <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the observation</t>
+  </si>
+  <si>
+    <t>Comments about the observation or the results.</t>
+  </si>
+  <si>
+    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
+  </si>
+  <si>
+    <t>Need to be able to provide free text additional information.</t>
+  </si>
+  <si>
+    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
+  </si>
+  <si>
+    <t>subjectOf.observationEvent[code="annotation"].value</t>
+  </si>
+  <si>
+    <t>Observation.bodySite</t>
+  </si>
+  <si>
+    <t>Observed body part</t>
+  </si>
+  <si>
+    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>How it was done</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>Methods for simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+  </si>
+  <si>
+    <t>OBX-17</t>
+  </si>
+  <si>
+    <t>methodCode</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-specimen)
+</t>
+  </si>
+  <si>
+    <t>Specimen used for this observation</t>
+  </si>
+  <si>
+    <t>The specimen that was used when this observation was made.</t>
+  </si>
+  <si>
+    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>&lt; 123038009 |Specimen|</t>
+  </si>
+  <si>
+    <t>SPM segment</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SPC].specimen</t>
+  </si>
+  <si>
+    <t>704319004 |Inherent in|</t>
+  </si>
+  <si>
+    <t>Observation.device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
+</t>
+  </si>
+  <si>
+    <t>(Measurement) Device</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
+  </si>
+  <si>
+    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
+  </si>
+  <si>
+    <t>&lt; 49062001 |Device|</t>
+  </si>
+  <si>
+    <t>OBX-17 / PRT -10</t>
+  </si>
+  <si>
+    <t>participation[typeCode=DEV]</t>
+  </si>
+  <si>
+    <t>424226004 |Using device|</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
+  </si>
+  <si>
+    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+  </si>
+  <si>
+    <t>OBX.7</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -757,555 +1155,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.subject.extension</t>
+    <t>Observation.referenceRange.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.subject.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Observation.subject.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Observation.subject.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Observation.subject.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter)
-</t>
-  </si>
-  <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
-</t>
-  </si>
-  <si>
-    <t>dateTime
-Period</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].id</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].extension:data-absent-reason</t>
-  </si>
-  <si>
-    <t>data-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
-</t>
-  </si>
-  <si>
-    <t>effective[x] absence reason</t>
-  </si>
-  <si>
-    <t>Provides a reason why the effectiveTime is missing.</t>
-  </si>
-  <si>
-    <t>ANY.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-organization|CareTeam|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>&lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-coded-values-laboratory-pathology-uv-ips</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
-  </si>
-  <si>
-    <t>value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abnormal Flag
-</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-observationinterpretation</t>
-  </si>
-  <si>
-    <t>Observation.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments about the observation</t>
-  </si>
-  <si>
-    <t>Comments about the observation or the results.</t>
-  </si>
-  <si>
-    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
-  </si>
-  <si>
-    <t>Need to be able to provide free text additional information.</t>
-  </si>
-  <si>
-    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
-  </si>
-  <si>
-    <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observed body part</t>
-  </si>
-  <si>
-    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
-  </si>
-  <si>
-    <t>&lt; 123037004 |Body structure|</t>
-  </si>
-  <si>
-    <t>OBX-20</t>
-  </si>
-  <si>
-    <t>targetSiteCode</t>
-  </si>
-  <si>
-    <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>How it was done</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
-  </si>
-  <si>
-    <t>OBX-17</t>
-  </si>
-  <si>
-    <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-specimen)
-</t>
-  </si>
-  <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
-  </si>
-  <si>
-    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
-  </si>
-  <si>
-    <t>&lt; 123038009 |Specimen|</t>
-  </si>
-  <si>
-    <t>SPM segment</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SPC].specimen</t>
-  </si>
-  <si>
-    <t>704319004 |Inherent in|</t>
-  </si>
-  <si>
-    <t>Observation.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
-</t>
-  </si>
-  <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
-  </si>
-  <si>
-    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>&lt; 49062001 |Device|</t>
-  </si>
-  <si>
-    <t>OBX-17 / PRT -10</t>
-  </si>
-  <si>
-    <t>participation[typeCode=DEV]</t>
-  </si>
-  <si>
-    <t>424226004 |Using device|</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
-  </si>
-  <si>
-    <t>OBX.7</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1393,9 +1249,6 @@
     <t>OBX-10</t>
   </si>
   <si>
-    <t>interpretationCode</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
@@ -1458,10 +1311,10 @@
     <t>Related resource that belongs to the Observation group</t>
   </si>
   <si>
-    <t>A reference to another Observation profiled by Observation-results-laboratory-pathology-uv-ips. The target observation (for instance an individual test member of a panel) is considered as a sub-observation of the current one, which plays the role of a grouper.</t>
-  </si>
-  <si>
-    <t>This element is used in the context of international patient summary when there is a need to group a collection of observations, because they belong to the same panel, or because they share a common interpretation comment, or a common media attachment (illustrative image or graph). In these cases, the current observation is the grouper, and its set of sub-observations are related observations using the type "has-member".  For a discussion on the ways Observations can be assembled in groups together see [Observation Grouping](http://hl7.org/fhir/observation.html#obsgrouping).</t>
+    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+  </si>
+  <si>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1535,17 +1388,7 @@
 &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
     <t>Actual component result</t>
@@ -1574,24 +1417,6 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values|</t>
-  </si>
-  <si>
-    <t>OBX-8</t>
-  </si>
-  <si>
-    <t>363713009 |Has interpretation|</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1729,21 +1554,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1917,14 +1727,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.09375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="34.5390625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
@@ -1948,7 +1758,7 @@
     <col min="26" max="26" width="86.34375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -2091,7 +1901,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2211,7 +2021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>91</v>
       </c>
@@ -2331,7 +2141,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>99</v>
       </c>
@@ -2449,7 +2259,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>105</v>
       </c>
@@ -2569,7 +2379,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>111</v>
       </c>
@@ -2689,7 +2499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>120</v>
       </c>
@@ -2809,7 +2619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>128</v>
       </c>
@@ -2929,7 +2739,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>136</v>
       </c>
@@ -3049,7 +2859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>144</v>
       </c>
@@ -3171,7 +2981,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>149</v>
       </c>
@@ -3291,7 +3101,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3411,7 +3221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>167</v>
       </c>
@@ -3531,7 +3341,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>176</v>
       </c>
@@ -3542,9 +3352,7 @@
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="E14" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>92</v>
       </c>
@@ -3564,16 +3372,16 @@
         <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3598,9 +3406,11 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
         <v>183</v>
       </c>
@@ -3653,7 +3463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>189</v>
       </c>
@@ -3666,7 +3476,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
@@ -3728,14 +3538,16 @@
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>189</v>
@@ -3762,27 +3574,25 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="B16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3792,28 +3602,28 @@
         <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3823,29 +3633,27 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3862,13 +3670,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3877,65 +3685,65 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3960,11 +3768,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3982,45 +3792,45 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4028,13 +3838,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
@@ -4043,20 +3853,18 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4104,13 +3912,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -4119,25 +3927,25 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>229</v>
       </c>
@@ -4146,7 +3954,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4162,19 +3970,23 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4222,7 +4034,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4234,44 +4046,44 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4280,21 +4092,23 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4330,57 +4144,57 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4388,13 +4202,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
@@ -4403,16 +4217,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4462,7 +4276,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4471,7 +4285,7 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
@@ -4483,24 +4297,24 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4511,7 +4325,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4523,18 +4337,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4558,13 +4372,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4582,13 +4396,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4597,30 +4411,30 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4643,18 +4457,20 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>150</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4690,19 +4506,17 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4711,7 +4525,7 @@
         <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
@@ -4720,29 +4534,31 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4763,18 +4579,20 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4798,13 +4616,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4822,7 +4638,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4831,7 +4647,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4840,27 +4656,27 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4871,7 +4687,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4880,21 +4696,23 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>265</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4918,13 +4736,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4942,16 +4760,16 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4963,35 +4781,35 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5000,22 +4818,22 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5040,13 +4858,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5064,13 +4880,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5079,65 +4895,65 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5186,13 +5002,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5201,30 +5017,30 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5247,15 +5063,17 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5280,13 +5098,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5304,7 +5122,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5316,44 +5134,44 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>234</v>
+        <v>321</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5365,18 +5183,20 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>139</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5400,43 +5220,43 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5445,10 +5265,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5457,16 +5277,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5478,7 +5296,7 @@
         <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5487,15 +5305,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5544,45 +5364,45 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>332</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5602,19 +5422,19 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5664,7 +5484,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5682,27 +5502,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5710,32 +5530,34 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5784,7 +5606,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5796,33 +5618,33 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5842,23 +5664,19 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5894,17 +5712,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5913,52 +5733,50 @@
         <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5967,20 +5785,18 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6004,11 +5820,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6026,19 +5844,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6047,10 +5865,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>218</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6059,49 +5877,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>321</v>
+        <v>141</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>322</v>
+        <v>147</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6150,49 +5966,47 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>328</v>
+        <v>135</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6204,29 +6018,25 @@
         <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6274,7 +6084,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6283,7 +6093,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6292,27 +6102,27 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6335,20 +6145,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>381</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6372,13 +6178,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6396,7 +6202,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6405,7 +6211,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6417,10 +6223,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6429,23 +6235,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6460,16 +6266,16 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>211</v>
+        <v>385</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>386</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6494,11 +6300,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6516,16 +6324,16 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6534,13 +6342,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>217</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>218</v>
+        <v>302</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6549,12 +6357,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6577,19 +6385,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6614,13 +6422,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6638,7 +6446,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6656,13 +6464,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6671,12 +6479,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6699,18 +6507,18 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6734,13 +6542,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6758,7 +6566,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6776,27 +6584,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>370</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6819,20 +6627,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6856,13 +6660,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6880,7 +6684,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6901,10 +6705,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6913,12 +6717,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6929,7 +6733,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6938,19 +6742,19 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7000,13 +6804,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7018,27 +6822,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7049,7 +6853,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7058,19 +6862,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7120,13 +6924,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7138,27 +6942,27 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7178,22 +6982,22 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7242,7 +7046,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7254,7 +7058,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>405</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7263,10 +7067,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7275,12 +7079,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7303,13 +7107,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>231</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>232</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7360,7 +7164,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>233</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7384,7 +7188,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7393,12 +7197,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7427,7 +7231,7 @@
         <v>139</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7480,7 +7284,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7504,7 +7308,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7513,16 +7317,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7544,10 +7348,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7602,7 +7406,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7635,12 +7439,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7648,7 +7452,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
@@ -7660,19 +7464,23 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>416</v>
+        <v>201</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7696,13 +7504,11 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7720,16 +7526,16 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7738,27 +7544,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>420</v>
+        <v>209</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>421</v>
+        <v>210</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7778,19 +7584,23 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7826,19 +7636,17 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7847,7 +7655,7 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7856,29 +7664,31 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>425</v>
+        <v>279</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7896,22 +7706,22 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>428</v>
+        <v>271</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>430</v>
+        <v>273</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7936,13 +7746,11 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>432</v>
+        <v>283</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7960,7 +7768,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7978,27 +7786,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>434</v>
+        <v>278</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>435</v>
+        <v>279</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8009,7 +7817,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8021,19 +7829,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>440</v>
+        <v>288</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8058,13 +7866,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>365</v>
+        <v>195</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>441</v>
+        <v>289</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>442</v>
+        <v>290</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8082,16 +7890,16 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8100,13 +7908,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>434</v>
+        <v>135</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>435</v>
+        <v>292</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8115,23 +7923,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8143,17 +7951,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>444</v>
+        <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>295</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>447</v>
+        <v>298</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8178,13 +7988,11 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8202,13 +8010,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8220,27 +8028,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8251,7 +8059,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8263,16 +8071,20 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="N53" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8320,13 +8132,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8341,1485 +8153,19 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>452</v>
+        <v>358</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y60" s="2"/>
-      <c r="Z60" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AC61" s="2"/>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y62" s="2"/>
-      <c r="Z62" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y64" s="2"/>
-      <c r="Z64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP65">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationresultslaboratorypathology</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationresultslaboratorypathology</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -826,7 +826,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-organization|CareTeam|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|CareTeam|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-observationinterpretation</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-observationinterpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1054,7 +1054,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-specimen)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen)
 </t>
   </si>
   <si>
@@ -1304,7 +1304,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationresultslaboratorypathology)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationresultslaboratorypathology)
 </t>
   </si>
   <si>
@@ -1755,7 +1755,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="86.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.55859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|DeviceRequest|ImmunizationRecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationadministration|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationdispense|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationstatement|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy)
 </t>
   </si>
   <si>
@@ -684,7 +684,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Group|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|Location)
 </t>
   </si>
   <si>
@@ -1105,7 +1105,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1345,7 +1345,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy|Media|QuestionnaireResponse|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1767,7 +1767,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="245.62890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -973,7 +973,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-observationinterpretation</t>
+    <t>https://termgit.elga.gv.at/ValueSet/at-aps-observationinterpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
